--- a/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
   </si>
@@ -33,9 +33,6 @@
   </si>
   <si>
     <t>STT</t>
-  </si>
-  <si>
-    <t>Chúng tôi cam kết hoàn toàn chịu trách nhiệm trước pháp luật về tính chính xác, trung thực của nội dung nêu trên và thực hiện theo đúng quy định của pháp luật.</t>
   </si>
   <si>
     <t>XXXXXXXXX</t>
@@ -105,20 +102,6 @@
     <t>Thuế GTGT</t>
   </si>
   <si>
-    <r>
-      <t>Lý do</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>: sai thông tin khách hàng sửa lại: Khách lẻ không lấy hóa đơn (Tiki) và địa chỉ 29/1 đường số 4, khu phố 3, phường Bình Khánh, quận 2, tp.HCM. </t>
-    </r>
-  </si>
-  <si>
     <t>ĐẠI DIỆN BÊN A</t>
   </si>
   <si>
@@ -128,10 +111,6 @@
     <t>(Chữ ký số, chữ ký điện tử)</t>
   </si>
   <si>
-    <t xml:space="preserve">
- </t>
-  </si>
-  <si>
     <t>Signature Valid</t>
   </si>
   <si>
@@ -139,13 +118,22 @@
   </si>
   <si>
     <t>Ký ngày:</t>
+  </si>
+  <si>
+    <t>Chúng tôi cam kết hoàn toàn chịu trách nhiệm trước pháp luật về tính chính xác, trung thực của nội dung nêu trên và thực hiện</t>
+  </si>
+  <si>
+    <t>MCCQT</t>
+  </si>
+  <si>
+    <t>theo đúng quy định của pháp luật.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,16 +189,22 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <i/>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <i/>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -223,7 +217,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -339,35 +333,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -396,9 +366,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -420,162 +387,150 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,6 +547,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1161393</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>99849</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1702676</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>42982</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1529255" y="7420304"/>
+          <a:ext cx="541283" cy="374057"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -858,63 +862,63 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.6640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="2.21875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="3.6640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="7.77734375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="18.88671875" style="4" customWidth="1"/>
-    <col min="8" max="9" width="8.6640625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="18.77734375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="1.44140625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="29.109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10" style="4" customWidth="1"/>
+    <col min="8" max="9" width="9.77734375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" style="4" customWidth="1"/>
     <col min="11" max="11" width="1.6640625" style="4" customWidth="1"/>
     <col min="12" max="16384" width="8.77734375" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="17"/>
+      <c r="B1" s="16"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="9"/>
-      <c r="C2" s="63" t="s">
+      <c r="C2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -924,8 +928,8 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
-      <c r="G4" s="20" t="s">
-        <v>5</v>
+      <c r="G4" s="17" t="s">
+        <v>4</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -939,7 +943,7 @@
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="20"/>
+      <c r="G5" s="17"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
@@ -947,149 +951,149 @@
     </row>
     <row r="6" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="B6" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
+      <c r="B7" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
       <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
-      <c r="B9" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55"/>
+      <c r="B9" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
       <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
       <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
-      <c r="B11" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
+      <c r="B11" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
       <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
-      <c r="B13" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
+      <c r="B13" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
+      <c r="B15" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="23"/>
+      <c r="B16" s="20"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -1102,446 +1106,451 @@
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
-      <c r="B17" s="50" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
+      <c r="B17" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
       <c r="K17" s="7"/>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
-      <c r="B18" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
+      <c r="B18" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
       <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
       <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
       <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="50"/>
+      <c r="B22" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
       <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
+      <c r="B23" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
       <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="52"/>
-      <c r="J24" s="52"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
-      <c r="B25" s="51" t="s">
+      <c r="B25" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
       <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="B27" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
+      <c r="B27" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
       <c r="K27" s="7"/>
     </row>
     <row r="28" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5"/>
-      <c r="B29" s="64" t="s">
+      <c r="B29" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="64"/>
-      <c r="D29" s="27" t="s">
+      <c r="C29" s="52"/>
+      <c r="D29" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="G29" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="26" t="s">
+      <c r="H29" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="I29" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="56" t="s">
         <v>23</v>
-      </c>
-      <c r="H29" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="I29" s="62"/>
-      <c r="J29" s="25" t="s">
-        <v>24</v>
       </c>
       <c r="K29" s="7"/>
     </row>
     <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="65"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="10"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="28"/>
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="32"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="24"/>
       <c r="K31" s="7"/>
     </row>
     <row r="32" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
-      <c r="B32" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="66"/>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="66"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
       <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="32"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="24"/>
       <c r="K33" s="7"/>
     </row>
-    <row r="34" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
-      <c r="B34" s="52" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
+      <c r="B34" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="48"/>
       <c r="K34" s="7"/>
     </row>
-    <row r="35" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
-      <c r="I35" s="59"/>
-      <c r="J35" s="59"/>
+      <c r="B35" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="51"/>
       <c r="K35" s="7"/>
     </row>
-    <row r="36" spans="1:12" s="13" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="11"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="68" t="s">
+    <row r="36" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
+      <c r="K36" s="7"/>
+    </row>
+    <row r="37" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="10"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="11"/>
+    </row>
+    <row r="38" spans="1:12" s="12" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="10"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="68" t="s">
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" s="49"/>
+      <c r="J38" s="49"/>
+      <c r="K38" s="11"/>
+    </row>
+    <row r="39" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="10"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="11"/>
+    </row>
+    <row r="40" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="I36" s="68"/>
-      <c r="J36" s="68"/>
-      <c r="K36" s="12"/>
-    </row>
-    <row r="37" spans="1:12" s="13" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="67" t="s">
+      <c r="E40" s="57"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="59"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="10"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="67" t="s">
-        <v>29</v>
-      </c>
-      <c r="I37" s="67"/>
-      <c r="J37" s="67"/>
-      <c r="K37" s="12"/>
-    </row>
-    <row r="38" spans="1:12" s="13" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="12"/>
-    </row>
-    <row r="39" spans="1:12" s="13" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="69"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="46"/>
-      <c r="J39" s="47"/>
-      <c r="K39" s="36"/>
-      <c r="L39" s="21"/>
-    </row>
-    <row r="40" spans="1:12" s="13" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="40" t="s">
+      <c r="E41" s="65"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="47"/>
+      <c r="J41" s="47"/>
+      <c r="K41" s="61"/>
+      <c r="L41" s="26"/>
+    </row>
+    <row r="42" spans="1:12" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="10"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E40" s="40"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="J40" s="41"/>
-      <c r="K40" s="35"/>
-      <c r="L40" s="34"/>
-    </row>
-    <row r="41" spans="1:12" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="I41" s="48"/>
-      <c r="J41" s="49"/>
-      <c r="K41" s="37"/>
-      <c r="L41" s="6"/>
-    </row>
-    <row r="42" spans="1:12" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="10"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="12"/>
-    </row>
-    <row r="43" spans="1:12" s="13" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="14"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="15"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="46"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="6"/>
+    </row>
+    <row r="43" spans="1:12" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="11"/>
+    </row>
+    <row r="44" spans="1:12" s="12" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="13"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="H19:J19"/>
+  <mergeCells count="37">
+    <mergeCell ref="B34:J34"/>
     <mergeCell ref="B28:J28"/>
+    <mergeCell ref="C38:E38"/>
     <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="H36:J36"/>
     <mergeCell ref="H37:J37"/>
-    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="D41:E41"/>
     <mergeCell ref="H1:J1"/>
-    <mergeCell ref="H29:I29"/>
     <mergeCell ref="C2:J2"/>
     <mergeCell ref="C3:J3"/>
     <mergeCell ref="C8:J8"/>
     <mergeCell ref="H20:J20"/>
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="B32:J32"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B17:J17"/>
     <mergeCell ref="B18:J18"/>
@@ -1551,22 +1560,20 @@
     <mergeCell ref="B9:J9"/>
     <mergeCell ref="B11:J11"/>
     <mergeCell ref="B13:J13"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:J32"/>
     <mergeCell ref="B22:J22"/>
     <mergeCell ref="B23:J23"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="H25:J25"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="B39:F39"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
   </si>
@@ -95,10 +95,6 @@
     <t xml:space="preserve">Số tiền trước thuế </t>
   </si>
   <si>
-    <t xml:space="preserve">Thành tiền
-</t>
-  </si>
-  <si>
     <t>Thuế GTGT</t>
   </si>
   <si>
@@ -123,10 +119,10 @@
     <t>Chúng tôi cam kết hoàn toàn chịu trách nhiệm trước pháp luật về tính chính xác, trung thực của nội dung nêu trên và thực hiện</t>
   </si>
   <si>
-    <t>MCCQT</t>
-  </si>
-  <si>
     <t>theo đúng quy định của pháp luật.</t>
+  </si>
+  <si>
+    <t>Thành tiền</t>
   </si>
 </sst>
 </file>
@@ -217,7 +213,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -333,11 +329,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -415,122 +424,125 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -559,8 +571,8 @@
       <xdr:rowOff>99849</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1702676</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>546538</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>42982</xdr:rowOff>
     </xdr:to>
@@ -868,11 +880,12 @@
     <col min="1" max="1" width="1.6640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="2.21875" style="4" customWidth="1"/>
     <col min="3" max="3" width="1.44140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="29.109375" style="4" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10" style="4" customWidth="1"/>
-    <col min="8" max="9" width="9.77734375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="4" customWidth="1"/>
     <col min="10" max="10" width="12.109375" style="4" customWidth="1"/>
     <col min="11" max="11" width="1.6640625" style="4" customWidth="1"/>
     <col min="12" max="16384" width="8.77734375" style="4"/>
@@ -886,54 +899,54 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="9"/>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="17" t="s">
+      <c r="B4" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -951,60 +964,60 @@
     </row>
     <row r="6" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
       <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
       <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1022,17 +1035,17 @@
     </row>
     <row r="11" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1050,17 +1063,17 @@
     </row>
     <row r="13" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1104,68 +1117,68 @@
       <c r="J16" s="6"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
       <c r="K17" s="7"/>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
       <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36" t="s">
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
       <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35" t="s">
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1181,68 +1194,68 @@
       <c r="J21" s="15"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
       <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
       <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36" t="s">
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
-      <c r="B25" s="35" t="s">
+      <c r="B25" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35" t="s">
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1275,57 +1288,55 @@
     </row>
     <row r="28" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
-      <c r="B29" s="52" t="s">
+      <c r="B29" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="52"/>
-      <c r="D29" s="53" t="s">
+      <c r="C29" s="61"/>
+      <c r="D29" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="55" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="56" t="s">
-        <v>23</v>
-      </c>
+      <c r="J29" s="63"/>
       <c r="K29" s="7"/>
     </row>
     <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="28"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="65"/>
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1343,15 +1354,15 @@
     </row>
     <row r="32" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
+      <c r="B32" s="60"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
       <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1369,32 +1380,32 @@
     </row>
     <row r="34" spans="1:12" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
-      <c r="B34" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="48"/>
+      <c r="B34" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="55"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="55"/>
+      <c r="J34" s="55"/>
       <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
-      <c r="B35" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="51"/>
+      <c r="B35" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
       <c r="K35" s="7"/>
     </row>
     <row r="36" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1404,44 +1415,44 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
       <c r="K36" s="7"/>
     </row>
     <row r="37" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
       <c r="B37" s="6"/>
-      <c r="C37" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
+      <c r="C37" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
       <c r="F37" s="25"/>
       <c r="G37" s="25"/>
-      <c r="H37" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
+      <c r="H37" s="57" t="s">
+        <v>25</v>
+      </c>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
       <c r="K37" s="11"/>
     </row>
     <row r="38" spans="1:12" s="12" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="6"/>
-      <c r="C38" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
+      <c r="C38" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
       <c r="F38" s="25"/>
       <c r="G38" s="25"/>
-      <c r="H38" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
+      <c r="H38" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
       <c r="K38" s="11"/>
     </row>
     <row r="39" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1460,33 +1471,33 @@
     <row r="40" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="22"/>
-      <c r="C40" s="59"/>
-      <c r="D40" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E40" s="57"/>
-      <c r="F40" s="62"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" s="31"/>
+      <c r="F40" s="37"/>
       <c r="G40" s="25"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="59"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="33"/>
       <c r="L40" s="18"/>
     </row>
     <row r="41" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="10"/>
-      <c r="B41" s="46"/>
-      <c r="C41" s="60"/>
-      <c r="D41" s="64" t="s">
-        <v>29</v>
-      </c>
-      <c r="E41" s="65"/>
-      <c r="F41" s="63"/>
+      <c r="B41" s="50"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="40"/>
+      <c r="F41" s="54"/>
       <c r="G41" s="25"/>
       <c r="H41" s="6"/>
-      <c r="I41" s="47"/>
-      <c r="J41" s="47"/>
-      <c r="K41" s="61"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="52"/>
+      <c r="K41" s="34"/>
       <c r="L41" s="26"/>
     </row>
     <row r="42" spans="1:12" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -1494,14 +1505,14 @@
       <c r="B42" s="6"/>
       <c r="C42" s="11"/>
       <c r="D42" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E42" s="8"/>
-      <c r="F42" s="10"/>
+      <c r="F42" s="14"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46"/>
+      <c r="I42" s="50"/>
+      <c r="J42" s="50"/>
       <c r="K42" s="11"/>
       <c r="L42" s="6"/>
     </row>
@@ -1532,7 +1543,7 @@
       <c r="K44" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="40">
     <mergeCell ref="B34:J34"/>
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="C38:E38"/>
@@ -1541,11 +1552,16 @@
     <mergeCell ref="H38:J38"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="H40:J40"/>
     <mergeCell ref="I41:J41"/>
     <mergeCell ref="I42:J42"/>
-    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D41:F41"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="C2:J2"/>
     <mergeCell ref="C3:J3"/>
@@ -1561,14 +1577,12 @@
     <mergeCell ref="B11:J11"/>
     <mergeCell ref="B13:J13"/>
     <mergeCell ref="H19:J19"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B4:J4"/>
     <mergeCell ref="B22:J22"/>
     <mergeCell ref="B23:J23"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="B25:G25"/>
-    <mergeCell ref="B29:C29"/>
     <mergeCell ref="H25:J25"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
   </si>
@@ -457,24 +457,72 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -492,54 +540,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -559,55 +559,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1161393</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>99849</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>546538</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>42982</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1529255" y="7420304"/>
-          <a:ext cx="541283" cy="374057"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -899,39 +850,39 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="9"/>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -964,60 +915,60 @@
     </row>
     <row r="6" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
       <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
       <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1035,17 +986,17 @@
     </row>
     <row r="11" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1063,17 +1014,17 @@
     </row>
     <row r="13" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="62"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1119,66 +1070,66 @@
     </row>
     <row r="17" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
       <c r="K17" s="7"/>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="59"/>
       <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40" t="s">
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39" t="s">
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
+      <c r="I20" s="59"/>
+      <c r="J20" s="59"/>
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1196,66 +1147,66 @@
     </row>
     <row r="22" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
       <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59"/>
       <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40" t="s">
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39" t="s">
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1288,23 +1239,23 @@
     </row>
     <row r="28" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
       <c r="K28" s="7"/>
     </row>
     <row r="29" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="61"/>
+      <c r="C29" s="46"/>
       <c r="D29" s="29" t="s">
         <v>19</v>
       </c>
@@ -1320,23 +1271,23 @@
       <c r="H29" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="I29" s="62" t="s">
+      <c r="I29" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="63"/>
+      <c r="J29" s="48"/>
       <c r="K29" s="7"/>
     </row>
     <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
-      <c r="B30" s="59"/>
-      <c r="C30" s="59"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
       <c r="D30" s="28"/>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
       <c r="G30" s="36"/>
       <c r="H30" s="36"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="65"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="50"/>
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1354,15 +1305,15 @@
     </row>
     <row r="32" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
-      <c r="B32" s="60"/>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="60"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
       <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1380,32 +1331,32 @@
     </row>
     <row r="34" spans="1:12" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
-      <c r="B34" s="55" t="s">
+      <c r="B34" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="55"/>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="55"/>
-      <c r="H34" s="55"/>
-      <c r="I34" s="55"/>
-      <c r="J34" s="55"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="56"/>
       <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
-      <c r="B35" s="58" t="s">
+      <c r="B35" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
       <c r="K35" s="7"/>
     </row>
     <row r="36" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1415,44 +1366,44 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
       <c r="K36" s="7"/>
     </row>
     <row r="37" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
       <c r="B37" s="6"/>
-      <c r="C37" s="57" t="s">
+      <c r="C37" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
       <c r="F37" s="25"/>
       <c r="G37" s="25"/>
-      <c r="H37" s="57" t="s">
+      <c r="H37" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="41"/>
       <c r="K37" s="11"/>
     </row>
     <row r="38" spans="1:12" s="12" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="6"/>
-      <c r="C38" s="56" t="s">
+      <c r="C38" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
       <c r="F38" s="25"/>
       <c r="G38" s="25"/>
-      <c r="H38" s="56" t="s">
+      <c r="H38" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
       <c r="K38" s="11"/>
     </row>
     <row r="39" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1478,25 +1429,29 @@
       <c r="E40" s="31"/>
       <c r="F40" s="37"/>
       <c r="G40" s="25"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
+      <c r="H40" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40" s="31"/>
+      <c r="J40" s="37"/>
       <c r="K40" s="33"/>
       <c r="L40" s="18"/>
     </row>
-    <row r="41" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" s="12" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="10"/>
-      <c r="B41" s="50"/>
-      <c r="C41" s="51"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="52"/>
       <c r="D41" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="E41" s="40"/>
-      <c r="F41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="55"/>
       <c r="G41" s="25"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="52"/>
+      <c r="H41" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="I41" s="54"/>
+      <c r="J41" s="55"/>
       <c r="K41" s="34"/>
       <c r="L41" s="26"/>
     </row>
@@ -1510,9 +1465,11 @@
       <c r="E42" s="8"/>
       <c r="F42" s="14"/>
       <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="50"/>
-      <c r="J42" s="50"/>
+      <c r="H42" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I42" s="8"/>
+      <c r="J42" s="14"/>
       <c r="K42" s="11"/>
       <c r="L42" s="6"/>
     </row>
@@ -1543,8 +1500,33 @@
       <c r="K44" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="38">
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="H41:J41"/>
     <mergeCell ref="B34:J34"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B9:J9"/>
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="C37:E37"/>
@@ -1557,37 +1539,9 @@
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="H25:J25"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NODE\einvoicevn.com\resources\report\60\95\ex_04ss\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295E17C0-E406-4453-B559-F2FCC6B64013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7020"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
@@ -59,9 +60,6 @@
     <t>BÊN A (BÊN BÁN): CHI NHÁNH CÔNG TY TNHH CUCKOO VINA TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
   </si>
   <si>
-    <t>Địa chỉ:Tầng 10, Cao ốc the 67 (678), 67 đường Hoàng Văn Thái, Phường Tân Phú, Quận 7, TP. Hồ Chí Minh, Việt Nam.</t>
-  </si>
-  <si>
     <t>Mã số thuế: 0108515678-001</t>
   </si>
   <si>
@@ -77,9 +75,6 @@
     <t>BÊN B (BÊN MUA): Khách lẻ không lấy hóa đơn (Lazada)</t>
   </si>
   <si>
-    <t>Địa chỉ: Khách lẻ không lấy hóa đơn (Lazada)</t>
-  </si>
-  <si>
     <t>Hai bên thống nhất lập biên bản về việc Giải trình những sai sót cho danh sách hóa đơn sau đây:</t>
   </si>
   <si>
@@ -123,12 +118,18 @@
   </si>
   <si>
     <t>Thành tiền</t>
+  </si>
+  <si>
+    <t>Địa chỉ:Tầng 10, Cao ốc the 67 (678), 67 đường Hoàng Văn Thái, Phường Tân Phú, Quận 7, TP. Hồ Chí Minh, Việt Nam.464564564456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Địa chỉ: Khách lẻ không lấy hóa đơn (Lazada) asdadaaaaaaaaaaaaaaaaaaaaaaa dasssasd asd asdasdasdasd sasdasdasdasd asdas as </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -346,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -363,7 +364,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -372,56 +373,50 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -460,19 +455,67 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -495,54 +538,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -823,7 +818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L44"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -844,70 +839,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="16"/>
+      <c r="B1" s="14"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
-      <c r="B5" s="9"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="17"/>
+      <c r="G5" s="15"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
@@ -915,149 +907,148 @@
     </row>
     <row r="6" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
       <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
       <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
       <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
       <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="20"/>
+      <c r="B16" s="18"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -1070,424 +1061,402 @@
     </row>
     <row r="17" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
-      <c r="B18" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="59"/>
-      <c r="J18" s="59"/>
+      <c r="B18" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
       <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="54"/>
-      <c r="J19" s="54"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
       <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="59"/>
-      <c r="J20" s="59"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
       <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
+      <c r="B22" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
+      <c r="B23" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
       <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
-      <c r="B25" s="59" t="s">
+      <c r="B25" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
       <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="B27" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
+      <c r="B27" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
       <c r="K27" s="7"/>
     </row>
     <row r="28" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
       <c r="K28" s="7"/>
     </row>
     <row r="29" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
-      <c r="B29" s="46" t="s">
+      <c r="B29" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="46"/>
-      <c r="D29" s="29" t="s">
+      <c r="C29" s="60"/>
+      <c r="D29" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="35" t="s">
+      <c r="G29" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="35" t="s">
+      <c r="H29" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="G29" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="I29" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="J29" s="48"/>
+      <c r="I29" s="61" t="s">
+        <v>30</v>
+      </c>
+      <c r="J29" s="62"/>
       <c r="K29" s="7"/>
     </row>
     <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="50"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="64"/>
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="24"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="22"/>
       <c r="K31" s="7"/>
     </row>
     <row r="32" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
+      <c r="B32" s="59"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="59"/>
       <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="24"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="22"/>
       <c r="K33" s="7"/>
     </row>
     <row r="34" spans="1:12" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
-      <c r="B34" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="56"/>
+      <c r="B34" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="49"/>
+      <c r="I34" s="49"/>
+      <c r="J34" s="49"/>
       <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
-      <c r="B35" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
+      <c r="B35" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
       <c r="K35" s="7"/>
     </row>
     <row r="36" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
       <c r="K36" s="7"/>
     </row>
-    <row r="37" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="10"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="41" t="s">
+    <row r="37" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="C37" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="10"/>
+    </row>
+    <row r="38" spans="1:12" s="6" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="C38" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="41" t="s">
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="55"/>
+      <c r="J38" s="55"/>
+      <c r="K38" s="10"/>
+    </row>
+    <row r="39" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="K39" s="10"/>
+    </row>
+    <row r="40" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="I37" s="41"/>
-      <c r="J37" s="41"/>
-      <c r="K37" s="11"/>
-    </row>
-    <row r="38" spans="1:12" s="12" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="10"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="40" t="s">
+      <c r="E40" s="29"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="I40" s="29"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="16"/>
+    </row>
+    <row r="41" spans="1:12" s="6" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="40" t="s">
+      <c r="E41" s="38"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="11"/>
-    </row>
-    <row r="39" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="10"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="11"/>
-    </row>
-    <row r="40" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="10"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="32" t="s">
+      <c r="I41" s="38"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="24"/>
+    </row>
+    <row r="42" spans="1:12" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="31"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="38" t="s">
+      <c r="E42" s="8"/>
+      <c r="F42" s="12"/>
+      <c r="H42" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I40" s="31"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="33"/>
-      <c r="L40" s="18"/>
-    </row>
-    <row r="41" spans="1:12" s="12" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="10"/>
-      <c r="B41" s="51"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" s="54"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="I41" s="54"/>
-      <c r="J41" s="55"/>
-      <c r="K41" s="34"/>
-      <c r="L41" s="26"/>
-    </row>
-    <row r="42" spans="1:12" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="10"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="I42" s="8"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="6"/>
-    </row>
-    <row r="43" spans="1:12" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="10"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="11"/>
-    </row>
-    <row r="44" spans="1:12" s="12" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="10"/>
+    </row>
+    <row r="43" spans="1:12" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="K43" s="10"/>
+    </row>
+    <row r="44" spans="1:12" s="6" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="11"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -1497,20 +1466,22 @@
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
-      <c r="K44" s="14"/>
+      <c r="K44" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="H41:J41"/>
@@ -1527,18 +1498,16 @@
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="H25:J25"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NODE\einvoicevn.com\resources\report\60\95\ex_04ss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295E17C0-E406-4453-B559-F2FCC6B64013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304880B4-1386-4E7C-9654-1D842F3AF091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -130,7 +130,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,12 +193,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="8"/>
       <color rgb="FF000000"/>
@@ -425,9 +419,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -455,11 +446,77 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -470,74 +527,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -845,52 +839,52 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -907,59 +901,59 @@
     </row>
     <row r="6" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
       <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -977,17 +971,17 @@
     </row>
     <row r="11" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1005,17 +999,17 @@
     </row>
     <row r="13" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1061,66 +1055,66 @@
     </row>
     <row r="17" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
       <c r="K17" s="7"/>
     </row>
     <row r="18" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
       <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38" t="s">
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
       <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37" t="s">
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1138,66 +1132,66 @@
     </row>
     <row r="22" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
       <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56"/>
       <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38" t="s">
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37" t="s">
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1230,55 +1224,55 @@
     </row>
     <row r="28" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="7"/>
     </row>
     <row r="29" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
-      <c r="B29" s="60" t="s">
+      <c r="B29" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="60"/>
-      <c r="D29" s="27" t="s">
+      <c r="C29" s="43"/>
+      <c r="D29" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="F29" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="33" t="s">
+      <c r="G29" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="H29" s="28" t="s">
+      <c r="H29" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="61" t="s">
+      <c r="I29" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="J29" s="62"/>
+      <c r="J29" s="45"/>
       <c r="K29" s="7"/>
     </row>
     <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="26"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="64"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="64"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="47"/>
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1296,15 +1290,15 @@
     </row>
     <row r="32" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
-      <c r="B32" s="59"/>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="59"/>
-      <c r="J32" s="59"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
       <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1322,72 +1316,72 @@
     </row>
     <row r="34" spans="1:12" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
-      <c r="B34" s="49" t="s">
+      <c r="B34" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="49"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
       <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
-      <c r="B35" s="57" t="s">
+      <c r="B35" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
       <c r="K35" s="7"/>
     </row>
     <row r="36" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
       <c r="K36" s="7"/>
     </row>
     <row r="37" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
-      <c r="C37" s="56" t="s">
+      <c r="C37" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
       <c r="F37" s="23"/>
       <c r="G37" s="23"/>
-      <c r="H37" s="56" t="s">
+      <c r="H37" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="I37" s="56"/>
-      <c r="J37" s="56"/>
+      <c r="I37" s="38"/>
+      <c r="J37" s="38"/>
       <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:12" s="6" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
-      <c r="C38" s="55" t="s">
+      <c r="C38" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
       <c r="F38" s="23"/>
       <c r="G38" s="23"/>
-      <c r="H38" s="55" t="s">
+      <c r="H38" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="I38" s="55"/>
-      <c r="J38" s="55"/>
+      <c r="I38" s="37"/>
+      <c r="J38" s="37"/>
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1403,37 +1397,37 @@
     <row r="40" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
       <c r="B40" s="20"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="30" t="s">
+      <c r="C40" s="30"/>
+      <c r="D40" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="E40" s="29"/>
-      <c r="F40" s="35"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="34"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="36" t="s">
+      <c r="H40" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="I40" s="29"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="31"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="34"/>
+      <c r="K40" s="30"/>
       <c r="L40" s="16"/>
     </row>
     <row r="41" spans="1:12" s="6" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
-      <c r="B41" s="45"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="47" t="s">
+      <c r="B41" s="48"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="E41" s="38"/>
-      <c r="F41" s="48"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="52"/>
       <c r="G41" s="23"/>
-      <c r="H41" s="47" t="s">
+      <c r="H41" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="I41" s="38"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="32"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="52"/>
+      <c r="K41" s="31"/>
       <c r="L41" s="24"/>
     </row>
     <row r="42" spans="1:12" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -1470,18 +1464,16 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B22:J22"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="H41:J41"/>
@@ -1498,16 +1490,18 @@
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NODE\einvoicevn.com\resources\report\60\95\ex_04ss\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_04ss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295E17C0-E406-4453-B559-F2FCC6B64013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484EAEA1-8C52-4FF8-8525-4F4CC88AC0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
   </si>
@@ -48,9 +48,6 @@
     <t>- Căn cứ Nghị định 123/2020/NĐ-CP ngày 19/10/2020 của Chính phủ quy định về hóa đơn, chứng từ.</t>
   </si>
   <si>
-    <t>- Căn cứ Thông tư 78/2021/TT-BTC ngày 17/09/2021 của Bộ Tài chính hướng dẫn thực hiện Nghị định số 123/2020/NĐ-CP ngày 19 tháng 10 năm 2020 của Chính phủ quy định về hóa đơn, chứng từ.</t>
-  </si>
-  <si>
     <t>- Căn cứ vào thỏa thuận giữa các bên.</t>
   </si>
   <si>
@@ -124,6 +121,12 @@
   </si>
   <si>
     <t xml:space="preserve">Địa chỉ: Khách lẻ không lấy hóa đơn (Lazada) asdadaaaaaaaaaaaaaaaaaaaaaaa dasssasd asd asdasdasdasd sasdasdasdasd asdas as </t>
+  </si>
+  <si>
+    <t>- Căn cứ Nghị định 70/2025/NĐ-CP ngày 20/03/2025 của Chính phủ sửa đổi, bổ sung một số điều của Nghị đinh 123/2020/NĐ-CP ngày 19/10/2020 của Chính phủ quy định về hóa đơn, chứng từ.</t>
+  </si>
+  <si>
+    <t>- Căn cứ Thông tư 32/2025/TT-BTC ngày 31/05/2025 của Bộ Tài chính hướng dẫn thực hiện Nghị định số 123/2020/NĐ-CP ngày 19/10/2020 của Chính phủ quy định về hóa đơn, chứng từ, Nghị định số 70/NĐ-CP/2025 ngày 20/03/2025 sửa đổi, bổ sung một số điều Nghị định số 123/2020/NĐ-CP.</t>
   </si>
 </sst>
 </file>
@@ -455,11 +458,77 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -470,74 +539,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -820,24 +823,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L44"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.6640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="2.21875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="1.44140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13.21875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="1.6640625" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="8.77734375" style="4"/>
+    <col min="1" max="1" width="1.6328125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="2.1796875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="1.453125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.6328125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="13.08984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="12.08984375" style="4" customWidth="1"/>
+    <col min="11" max="11" width="1.6328125" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="8.81640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="8" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="14"/>
       <c r="C1" s="2"/>
@@ -845,55 +848,55 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
       <c r="K1" s="3"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="9.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="9.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -905,64 +908,64 @@
       <c r="J5" s="6"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -975,22 +978,22 @@
       <c r="J10" s="17"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
-      <c r="B11" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
+      <c r="B11" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="62"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -1003,311 +1006,313 @@
       <c r="J12" s="17"/>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="5"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5"/>
+      <c r="B15" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="5"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="7"/>
-    </row>
-    <row r="14" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="7"/>
-    </row>
-    <row r="15" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="18" t="s">
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" ht="7.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="5"/>
+      <c r="B19" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="7"/>
-    </row>
-    <row r="16" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="7"/>
-    </row>
-    <row r="17" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="44" t="s">
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="5"/>
+      <c r="B20" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5"/>
+      <c r="B21" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="37" t="s">
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="7"/>
+    </row>
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="5"/>
+      <c r="B22" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="7"/>
+    </row>
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="5"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="7"/>
+    </row>
+    <row r="24" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="5"/>
+      <c r="B24" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="7"/>
+    </row>
+    <row r="25" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="5"/>
+      <c r="B25" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="38" t="s">
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="7"/>
+    </row>
+    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="5"/>
+      <c r="B26" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38" t="s">
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="7"/>
+    </row>
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="5"/>
+      <c r="B27" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="37" t="s">
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="7"/>
-    </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="7"/>
-    </row>
-    <row r="22" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="44" t="s">
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="7"/>
+    </row>
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="5"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="7"/>
+    </row>
+    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="7"/>
-    </row>
-    <row r="23" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="7"/>
-    </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="7"/>
-    </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="7"/>
-    </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="7"/>
-    </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="18" t="s">
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="7"/>
+    </row>
+    <row r="30" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="5"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="7"/>
+    </row>
+    <row r="31" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="5"/>
+      <c r="B31" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="44"/>
+      <c r="D31" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="7"/>
-    </row>
-    <row r="28" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="7"/>
-    </row>
-    <row r="29" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
-      <c r="B29" s="60" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="60"/>
-      <c r="D29" s="27" t="s">
+      <c r="E31" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="F31" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="G31" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="33" t="s">
+      <c r="H31" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="H29" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="J29" s="62"/>
-      <c r="K29" s="7"/>
-    </row>
-    <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" spans="1:11" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="22"/>
+      <c r="I31" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" s="46"/>
       <c r="K31" s="7"/>
     </row>
-    <row r="32" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
-      <c r="B32" s="59"/>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="59"/>
-      <c r="J32" s="59"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="7"/>
     </row>
-    <row r="33" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="11.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
@@ -1320,194 +1325,222 @@
       <c r="J33" s="22"/>
       <c r="K33" s="7"/>
     </row>
-    <row r="34" spans="1:12" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
-      <c r="B34" s="49" t="s">
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="7"/>
+    </row>
+    <row r="35" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="5"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="7"/>
+    </row>
+    <row r="36" spans="1:12" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="5"/>
+      <c r="B36" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="7"/>
+    </row>
+    <row r="37" spans="1:12" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="5"/>
+      <c r="B37" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="49"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
-      <c r="K34" s="7"/>
-    </row>
-    <row r="35" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="57" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="7"/>
-    </row>
-    <row r="36" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="7"/>
-    </row>
-    <row r="37" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
-      <c r="C37" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="I37" s="56"/>
-      <c r="J37" s="56"/>
-      <c r="K37" s="10"/>
-    </row>
-    <row r="38" spans="1:12" s="6" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-      <c r="C38" s="55" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="55" t="s">
-        <v>24</v>
-      </c>
-      <c r="I38" s="55"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="10"/>
-    </row>
-    <row r="39" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="41"/>
+      <c r="K37" s="7"/>
+    </row>
+    <row r="38" spans="1:12" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="5"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="7"/>
+    </row>
+    <row r="39" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
+      <c r="C39" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
       <c r="F39" s="23"/>
       <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
+      <c r="H39" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
       <c r="K39" s="10"/>
     </row>
-    <row r="40" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" s="6" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="30" t="s">
+      <c r="C40" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="38"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="10"/>
+    </row>
+    <row r="41" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="9"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="K41" s="10"/>
+    </row>
+    <row r="42" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="9"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="29"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="29"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="16"/>
+    </row>
+    <row r="43" spans="1:12" s="6" customFormat="1" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="9"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="E40" s="29"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="36" t="s">
+      <c r="E43" s="52"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="I40" s="29"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="16"/>
-    </row>
-    <row r="41" spans="1:12" s="6" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="45"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="47" t="s">
+      <c r="I43" s="52"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="24"/>
+    </row>
+    <row r="44" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E41" s="38"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="47" t="s">
+      <c r="E44" s="8"/>
+      <c r="F44" s="12"/>
+      <c r="H44" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I41" s="38"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="24"/>
-    </row>
-    <row r="42" spans="1:12" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="12"/>
-      <c r="H42" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42" s="8"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="10"/>
-    </row>
-    <row r="43" spans="1:12" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="K43" s="10"/>
-    </row>
-    <row r="44" spans="1:12" s="6" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
       <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="10"/>
+    </row>
+    <row r="45" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="9"/>
+      <c r="K45" s="10"/>
+    </row>
+    <row r="46" spans="1:12" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="11"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="B34:J34"/>
+  <mergeCells count="40">
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="B36:J36"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="C2:J2"/>
     <mergeCell ref="C3:J3"/>
     <mergeCell ref="C8:J8"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B19:J19"/>
+    <mergeCell ref="B20:J20"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NODE\einvoicevn.com\resources\report\60\95\ex_04ss\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_04ss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304880B4-1386-4E7C-9654-1D842F3AF091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484EAEA1-8C52-4FF8-8525-4F4CC88AC0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
   </si>
@@ -48,9 +48,6 @@
     <t>- Căn cứ Nghị định 123/2020/NĐ-CP ngày 19/10/2020 của Chính phủ quy định về hóa đơn, chứng từ.</t>
   </si>
   <si>
-    <t>- Căn cứ Thông tư 78/2021/TT-BTC ngày 17/09/2021 của Bộ Tài chính hướng dẫn thực hiện Nghị định số 123/2020/NĐ-CP ngày 19 tháng 10 năm 2020 của Chính phủ quy định về hóa đơn, chứng từ.</t>
-  </si>
-  <si>
     <t>- Căn cứ vào thỏa thuận giữa các bên.</t>
   </si>
   <si>
@@ -124,13 +121,19 @@
   </si>
   <si>
     <t xml:space="preserve">Địa chỉ: Khách lẻ không lấy hóa đơn (Lazada) asdadaaaaaaaaaaaaaaaaaaaaaaa dasssasd asd asdasdasdasd sasdasdasdasd asdas as </t>
+  </si>
+  <si>
+    <t>- Căn cứ Nghị định 70/2025/NĐ-CP ngày 20/03/2025 của Chính phủ sửa đổi, bổ sung một số điều của Nghị đinh 123/2020/NĐ-CP ngày 19/10/2020 của Chính phủ quy định về hóa đơn, chứng từ.</t>
+  </si>
+  <si>
+    <t>- Căn cứ Thông tư 32/2025/TT-BTC ngày 31/05/2025 của Bộ Tài chính hướng dẫn thực hiện Nghị định số 123/2020/NĐ-CP ngày 19/10/2020 của Chính phủ quy định về hóa đơn, chứng từ, Nghị định số 70/NĐ-CP/2025 ngày 20/03/2025 sửa đổi, bổ sung một số điều Nghị định số 123/2020/NĐ-CP.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +196,12 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <b/>
       <sz val="8"/>
       <color rgb="FF000000"/>
@@ -419,6 +428,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -529,9 +541,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -814,24 +823,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L44"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.6640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="2.21875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="1.44140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13.21875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="1.6640625" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="8.77734375" style="4"/>
+    <col min="1" max="1" width="1.6328125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="2.1796875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="1.453125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.6328125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="13.08984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="12.08984375" style="4" customWidth="1"/>
+    <col min="11" max="11" width="1.6328125" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="8.81640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="8" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="14"/>
       <c r="C1" s="2"/>
@@ -839,55 +848,55 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
       <c r="K1" s="3"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="9.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="9.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -899,64 +908,64 @@
       <c r="J5" s="6"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
-      <c r="B9" s="59" t="s">
+      <c r="B9" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="59"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -969,22 +978,22 @@
       <c r="J10" s="17"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
-      <c r="B11" s="60" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
+      <c r="B11" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="62"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -997,311 +1006,313 @@
       <c r="J12" s="17"/>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="5"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5"/>
+      <c r="B15" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="5"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="7"/>
-    </row>
-    <row r="14" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="7"/>
-    </row>
-    <row r="15" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="18" t="s">
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" ht="7.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="5"/>
+      <c r="B19" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="7"/>
-    </row>
-    <row r="16" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="7"/>
-    </row>
-    <row r="17" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="36" t="s">
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="5"/>
+      <c r="B20" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5"/>
+      <c r="B21" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="56" t="s">
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="7"/>
+    </row>
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="5"/>
+      <c r="B22" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="7"/>
+    </row>
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="5"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="7"/>
+    </row>
+    <row r="24" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="5"/>
+      <c r="B24" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="7"/>
+    </row>
+    <row r="25" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="5"/>
+      <c r="B25" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="56"/>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="51" t="s">
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="7"/>
+    </row>
+    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="5"/>
+      <c r="B26" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51" t="s">
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="7"/>
+    </row>
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="5"/>
+      <c r="B27" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="56" t="s">
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="56"/>
-      <c r="J20" s="56"/>
-      <c r="K20" s="7"/>
-    </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="7"/>
-    </row>
-    <row r="22" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="36" t="s">
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="7"/>
+    </row>
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="5"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="7"/>
+    </row>
+    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="7"/>
-    </row>
-    <row r="23" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="56"/>
-      <c r="K23" s="7"/>
-    </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="7"/>
-    </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="56"/>
-      <c r="J25" s="56"/>
-      <c r="K25" s="7"/>
-    </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="7"/>
-    </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="18" t="s">
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="7"/>
+    </row>
+    <row r="30" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="5"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="7"/>
+    </row>
+    <row r="31" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="5"/>
+      <c r="B31" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="44"/>
+      <c r="D31" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="7"/>
-    </row>
-    <row r="28" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="7"/>
-    </row>
-    <row r="29" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
-      <c r="B29" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="43"/>
-      <c r="D29" s="26" t="s">
+      <c r="E31" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="32" t="s">
+      <c r="F31" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="32" t="s">
+      <c r="G31" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="32" t="s">
+      <c r="H31" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="H29" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="J29" s="45"/>
-      <c r="K29" s="7"/>
-    </row>
-    <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" spans="1:11" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="22"/>
+      <c r="I31" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" s="46"/>
       <c r="K31" s="7"/>
     </row>
-    <row r="32" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="42"/>
       <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="7"/>
     </row>
-    <row r="33" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="11.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
@@ -1314,194 +1325,222 @@
       <c r="J33" s="22"/>
       <c r="K33" s="7"/>
     </row>
-    <row r="34" spans="1:12" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
-      <c r="B34" s="53" t="s">
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="7"/>
+    </row>
+    <row r="35" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="5"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="7"/>
+    </row>
+    <row r="36" spans="1:12" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="5"/>
+      <c r="B36" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="7"/>
+    </row>
+    <row r="37" spans="1:12" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="5"/>
+      <c r="B37" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="7"/>
-    </row>
-    <row r="35" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="7"/>
-    </row>
-    <row r="36" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39"/>
-      <c r="K36" s="7"/>
-    </row>
-    <row r="37" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
-      <c r="C37" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="I37" s="38"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="10"/>
-    </row>
-    <row r="38" spans="1:12" s="6" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-      <c r="C38" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="I38" s="37"/>
-      <c r="J38" s="37"/>
-      <c r="K38" s="10"/>
-    </row>
-    <row r="39" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="41"/>
+      <c r="K37" s="7"/>
+    </row>
+    <row r="38" spans="1:12" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="5"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="7"/>
+    </row>
+    <row r="39" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
+      <c r="C39" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
       <c r="F39" s="23"/>
       <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
+      <c r="H39" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
       <c r="K39" s="10"/>
     </row>
-    <row r="40" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" s="6" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="29" t="s">
+      <c r="C40" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="38"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="10"/>
+    </row>
+    <row r="41" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="9"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="K41" s="10"/>
+    </row>
+    <row r="42" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="9"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="29"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="29"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="16"/>
+    </row>
+    <row r="43" spans="1:12" s="6" customFormat="1" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="9"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="E40" s="28"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="35" t="s">
+      <c r="E43" s="52"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="I40" s="28"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="16"/>
-    </row>
-    <row r="41" spans="1:12" s="6" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="48"/>
-      <c r="C41" s="49"/>
-      <c r="D41" s="50" t="s">
+      <c r="I43" s="52"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="24"/>
+    </row>
+    <row r="44" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E41" s="51"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="50" t="s">
+      <c r="E44" s="8"/>
+      <c r="F44" s="12"/>
+      <c r="H44" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I41" s="51"/>
-      <c r="J41" s="52"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="24"/>
-    </row>
-    <row r="42" spans="1:12" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="12"/>
-      <c r="H42" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42" s="8"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="10"/>
-    </row>
-    <row r="43" spans="1:12" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="K43" s="10"/>
-    </row>
-    <row r="44" spans="1:12" s="6" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
       <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="10"/>
+    </row>
+    <row r="45" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="9"/>
+      <c r="K45" s="10"/>
+    </row>
+    <row r="46" spans="1:12" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="11"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="H25:J25"/>
+  <mergeCells count="40">
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="H27:J27"/>
     <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B14:J14"/>
     <mergeCell ref="B13:J13"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="B36:J36"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="C2:J2"/>
     <mergeCell ref="C3:J3"/>
     <mergeCell ref="C8:J8"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B19:J19"/>
+    <mergeCell ref="B20:J20"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_04ss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484EAEA1-8C52-4FF8-8525-4F4CC88AC0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2CE6E5A-88AC-4571-AD02-54FC5C7CAC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Hai bên thống nhất lập biên bản về việc Giải trình những sai sót cho danh sách hóa đơn sau đây:</t>
   </si>
   <si>
-    <t>Ký hiệu HĐ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Số HĐ </t>
   </si>
   <si>
@@ -127,6 +124,12 @@
   </si>
   <si>
     <t>- Căn cứ Thông tư 32/2025/TT-BTC ngày 31/05/2025 của Bộ Tài chính hướng dẫn thực hiện Nghị định số 123/2020/NĐ-CP ngày 19/10/2020 của Chính phủ quy định về hóa đơn, chứng từ, Nghị định số 70/NĐ-CP/2025 ngày 20/03/2025 sửa đổi, bổ sung một số điều Nghị định số 123/2020/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Mẫu số HĐ</t>
+  </si>
+  <si>
+    <t>Ký hiệu HD</t>
   </si>
 </sst>
 </file>
@@ -217,7 +220,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -333,24 +336,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -437,9 +427,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -458,9 +445,60 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -468,9 +506,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -482,65 +517,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -829,13 +816,13 @@
     <col min="1" max="1" width="1.6328125" style="4" customWidth="1"/>
     <col min="2" max="2" width="2.1796875" style="4" customWidth="1"/>
     <col min="3" max="3" width="1.453125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.6328125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" style="4" customWidth="1"/>
     <col min="5" max="5" width="13.1796875" style="4" customWidth="1"/>
     <col min="6" max="6" width="12.1796875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="12.6328125" style="4" customWidth="1"/>
     <col min="8" max="8" width="13.08984375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="12.08984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.6328125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="16.08984375" style="4" customWidth="1"/>
     <col min="11" max="11" width="1.6328125" style="4" customWidth="1"/>
     <col min="12" max="16384" width="8.81640625" style="4"/>
   </cols>
@@ -848,52 +835,52 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="9.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="9.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -910,59 +897,59 @@
     </row>
     <row r="6" spans="1:11" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
       <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
       <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -980,17 +967,17 @@
     </row>
     <row r="11" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
-      <c r="B11" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
+      <c r="B11" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1008,45 +995,45 @@
     </row>
     <row r="13" spans="1:11" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
-      <c r="B13" s="61" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
+      <c r="B13" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
-      <c r="B14" s="61"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
-      <c r="B15" s="63" t="s">
+      <c r="B15" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1092,66 +1079,66 @@
     </row>
     <row r="19" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
       <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
-      <c r="B20" s="57" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
+      <c r="B20" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52" t="s">
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
       <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57" t="s">
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
       <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1169,66 +1156,66 @@
     </row>
     <row r="24" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
-      <c r="B25" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
+      <c r="B25" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52" t="s">
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="I26" s="52"/>
-      <c r="J26" s="52"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
       <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57" t="s">
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
       <c r="K27" s="7"/>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1261,55 +1248,57 @@
     </row>
     <row r="30" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="37"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
-      <c r="B31" s="44" t="s">
+      <c r="B31" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="44"/>
+      <c r="C31" s="59"/>
       <c r="D31" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="G31" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="F31" s="33" t="s">
+      <c r="H31" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="33" t="s">
+      <c r="I31" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="H31" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I31" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="J31" s="46"/>
+      <c r="J31" s="32" t="s">
+        <v>28</v>
+      </c>
       <c r="K31" s="7"/>
     </row>
     <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="57"/>
       <c r="D32" s="26"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="48"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
       <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="11.4" customHeight="1" x14ac:dyDescent="0.35">
@@ -1327,15 +1316,15 @@
     </row>
     <row r="34" spans="1:12" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
       <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
@@ -1353,72 +1342,72 @@
     </row>
     <row r="36" spans="1:12" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
-      <c r="B36" s="54" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="54"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="54"/>
-      <c r="I36" s="54"/>
-      <c r="J36" s="54"/>
+      <c r="B36" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
       <c r="K36" s="7"/>
     </row>
     <row r="37" spans="1:12" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
-      <c r="B37" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
-      <c r="J37" s="41"/>
+      <c r="B37" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="56"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
       <c r="K37" s="7"/>
     </row>
     <row r="38" spans="1:12" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
       <c r="K38" s="7"/>
     </row>
     <row r="39" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
-      <c r="C39" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
+      <c r="C39" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
       <c r="F39" s="23"/>
       <c r="G39" s="23"/>
-      <c r="H39" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
+      <c r="H39" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:12" s="6" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
-      <c r="C40" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
+      <c r="C40" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
       <c r="F40" s="23"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="I40" s="38"/>
-      <c r="J40" s="38"/>
+      <c r="H40" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="54"/>
+      <c r="J40" s="54"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1434,49 +1423,49 @@
     <row r="42" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9"/>
       <c r="B42" s="20"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="29"/>
-      <c r="F42" s="35"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="62"/>
+      <c r="F42" s="63"/>
       <c r="G42" s="23"/>
-      <c r="H42" s="36" t="s">
-        <v>24</v>
+      <c r="H42" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I42" s="29"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="31"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="30"/>
       <c r="L42" s="16"/>
     </row>
     <row r="43" spans="1:12" s="6" customFormat="1" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9"/>
-      <c r="B43" s="49"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="52"/>
-      <c r="F43" s="53"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="45"/>
+      <c r="D43" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="37"/>
+      <c r="F43" s="47"/>
       <c r="G43" s="23"/>
-      <c r="H43" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="I43" s="52"/>
-      <c r="J43" s="53"/>
-      <c r="K43" s="32"/>
+      <c r="H43" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="37"/>
+      <c r="J43" s="47"/>
+      <c r="K43" s="31"/>
       <c r="L43" s="24"/>
     </row>
     <row r="44" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9"/>
       <c r="C44" s="10"/>
       <c r="D44" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="12"/>
       <c r="H44" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I44" s="8"/>
       <c r="J44" s="12"/>
@@ -1500,19 +1489,18 @@
       <c r="K46" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="B13:J13"/>
+  <mergeCells count="39">
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="H43:J43"/>
@@ -1529,18 +1517,18 @@
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="B37:J37"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_04ss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2CE6E5A-88AC-4571-AD02-54FC5C7CAC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D68CFAF-98BE-4E77-99B4-9C27F9AA221F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -445,6 +445,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -499,6 +502,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -516,18 +528,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -835,52 +835,52 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="9.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="9.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -897,59 +897,59 @@
     </row>
     <row r="6" spans="1:11" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
       <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
       <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -967,17 +967,17 @@
     </row>
     <row r="11" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -995,45 +995,45 @@
     </row>
     <row r="13" spans="1:11" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1079,66 +1079,66 @@
     </row>
     <row r="19" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
       <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37" t="s">
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
       <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36" t="s">
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
       <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1156,66 +1156,66 @@
     </row>
     <row r="24" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37" t="s">
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
       <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36" t="s">
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
       <c r="K27" s="7"/>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1248,23 +1248,23 @@
     </row>
     <row r="30" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="59"/>
+      <c r="C31" s="63"/>
       <c r="D31" s="27" t="s">
         <v>33</v>
       </c>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
-      <c r="B32" s="57"/>
-      <c r="C32" s="57"/>
+      <c r="B32" s="61"/>
+      <c r="C32" s="61"/>
       <c r="D32" s="26"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="33"/>
+      <c r="G32" s="36"/>
       <c r="H32" s="33"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="60"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
       <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="11.4" customHeight="1" x14ac:dyDescent="0.35">
@@ -1316,15 +1316,15 @@
     </row>
     <row r="34" spans="1:12" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
-      <c r="B34" s="58"/>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="58"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="62"/>
       <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
@@ -1342,72 +1342,72 @@
     </row>
     <row r="36" spans="1:12" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
-      <c r="B36" s="48" t="s">
+      <c r="B36" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="49"/>
+      <c r="J36" s="49"/>
       <c r="K36" s="7"/>
     </row>
     <row r="37" spans="1:12" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
-      <c r="B37" s="56" t="s">
+      <c r="B37" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="56"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="60"/>
       <c r="K37" s="7"/>
     </row>
     <row r="38" spans="1:12" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="51"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
       <c r="K38" s="7"/>
     </row>
     <row r="39" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
-      <c r="C39" s="55" t="s">
+      <c r="C39" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
       <c r="F39" s="23"/>
       <c r="G39" s="23"/>
-      <c r="H39" s="55" t="s">
+      <c r="H39" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="59"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:12" s="6" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
-      <c r="C40" s="54" t="s">
+      <c r="C40" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="54"/>
-      <c r="E40" s="54"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
       <c r="F40" s="23"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="54" t="s">
+      <c r="H40" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="I40" s="54"/>
-      <c r="J40" s="54"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1424,11 +1424,11 @@
       <c r="A42" s="9"/>
       <c r="B42" s="20"/>
       <c r="C42" s="30"/>
-      <c r="D42" s="61" t="s">
+      <c r="D42" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="E42" s="62"/>
-      <c r="F42" s="63"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="57"/>
       <c r="G42" s="23"/>
       <c r="H42" s="35" t="s">
         <v>23</v>
@@ -1440,19 +1440,19 @@
     </row>
     <row r="43" spans="1:12" s="6" customFormat="1" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9"/>
-      <c r="B43" s="44"/>
-      <c r="C43" s="45"/>
-      <c r="D43" s="46" t="s">
+      <c r="B43" s="45"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="37"/>
-      <c r="F43" s="47"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="48"/>
       <c r="G43" s="23"/>
-      <c r="H43" s="46" t="s">
+      <c r="H43" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="I43" s="37"/>
-      <c r="J43" s="47"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="48"/>
       <c r="K43" s="31"/>
       <c r="L43" s="24"/>
     </row>

--- a/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_04ss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D68CFAF-98BE-4E77-99B4-9C27F9AA221F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79661296-AA5A-4AD7-BE0B-A5120A6BBB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -448,11 +448,74 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -463,71 +526,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -835,52 +835,52 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="9.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="9.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -897,59 +897,59 @@
     </row>
     <row r="6" spans="1:11" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
       <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -967,17 +967,17 @@
     </row>
     <row r="11" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -995,45 +995,45 @@
     </row>
     <row r="13" spans="1:11" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="59"/>
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" ht="10.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1079,66 +1079,66 @@
     </row>
     <row r="19" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
       <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38" t="s">
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
       <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37" t="s">
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
       <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1156,66 +1156,66 @@
     </row>
     <row r="24" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
-      <c r="B24" s="44" t="s">
+      <c r="B24" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38" t="s">
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
       <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
-      <c r="B27" s="37" t="s">
+      <c r="B27" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37" t="s">
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
       <c r="K27" s="7"/>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1248,23 +1248,23 @@
     </row>
     <row r="30" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="63"/>
+      <c r="C31" s="47"/>
       <c r="D31" s="27" t="s">
         <v>33</v>
       </c>
@@ -1290,8 +1290,8 @@
     </row>
     <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
-      <c r="B32" s="61"/>
-      <c r="C32" s="61"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
       <c r="D32" s="26"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
@@ -1316,15 +1316,15 @@
     </row>
     <row r="34" spans="1:12" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
-      <c r="B34" s="62"/>
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="62"/>
-      <c r="J34" s="62"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
       <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
@@ -1342,72 +1342,72 @@
     </row>
     <row r="36" spans="1:12" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
-      <c r="B36" s="49" t="s">
+      <c r="B36" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="49"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="49"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
       <c r="K36" s="7"/>
     </row>
     <row r="37" spans="1:12" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
-      <c r="B37" s="60" t="s">
+      <c r="B37" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="60"/>
-      <c r="D37" s="60"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="60"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="60"/>
-      <c r="J37" s="60"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
       <c r="K37" s="7"/>
     </row>
     <row r="38" spans="1:12" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
       <c r="K38" s="7"/>
     </row>
     <row r="39" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
-      <c r="C39" s="59" t="s">
+      <c r="C39" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
       <c r="F39" s="23"/>
       <c r="G39" s="23"/>
-      <c r="H39" s="59" t="s">
+      <c r="H39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="I39" s="59"/>
-      <c r="J39" s="59"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:12" s="6" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
-      <c r="C40" s="58" t="s">
+      <c r="C40" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
       <c r="F40" s="23"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="58" t="s">
+      <c r="H40" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I40" s="58"/>
-      <c r="J40" s="58"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="41"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:12" s="6" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1424,11 +1424,11 @@
       <c r="A42" s="9"/>
       <c r="B42" s="20"/>
       <c r="C42" s="30"/>
-      <c r="D42" s="55" t="s">
+      <c r="D42" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E42" s="56"/>
-      <c r="F42" s="57"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="39"/>
       <c r="G42" s="23"/>
       <c r="H42" s="35" t="s">
         <v>23</v>
@@ -1440,19 +1440,19 @@
     </row>
     <row r="43" spans="1:12" s="6" customFormat="1" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9"/>
-      <c r="B43" s="45"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="47" t="s">
+      <c r="B43" s="48"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="38"/>
-      <c r="F43" s="48"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="52"/>
       <c r="G43" s="23"/>
-      <c r="H43" s="47" t="s">
+      <c r="H43" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="I43" s="38"/>
-      <c r="J43" s="48"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="52"/>
       <c r="K43" s="31"/>
       <c r="L43" s="24"/>
     </row>
@@ -1490,17 +1490,18 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="B37:J37"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="B13:J13"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="H43:J43"/>
@@ -1517,18 +1518,17 @@
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0.75" header="0.3" footer="0.3"/>
